--- a/reports/report.xlsx
+++ b/reports/report.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37.05161600001156</v>
+        <v>37.99269880005158</v>
       </c>
     </row>
     <row r="3">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.84180910000578</v>
+        <v>22.14527960005216</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28.50361380004324</v>
+        <v>26.10934989992529</v>
       </c>
     </row>
     <row r="5">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28.58569550001994</v>
+        <v>27.35174189996906</v>
       </c>
     </row>
     <row r="6">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28.4995892001316</v>
+        <v>28.35954069998115</v>
       </c>
     </row>
     <row r="7">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27.29184930003248</v>
+        <v>26.23254909995012</v>
       </c>
     </row>
     <row r="8">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>26.88401550007984</v>
+        <v>28.20734920003451</v>
       </c>
     </row>
   </sheetData>

--- a/reports/report.xlsx
+++ b/reports/report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,97 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37.99269880005158</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>tests/test_genz_categories.py::TestGENZCategories::test_mens_tshirts_positive</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>22.14527960005216</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>tests/test_genz_categories.py::TestGENZCategories::test_mens_kurtas_positive</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>26.10934989992529</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>tests/test_genz_categories.py::TestGENZCategories::test_mens_shoes_positive</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>27.35174189996906</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>tests/test_genz_categories.py::TestGENZCategories::test_skincare_positive</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>28.35954069998115</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>tests/test_genz_categories.py::TestGENZCategories::test_jewellery_negative</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>26.23254909995012</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>tests/test_genz_categories.py::TestGENZCategories::test_heels_negative</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>28.20734920003451</v>
+        <v>40.61953580006957</v>
       </c>
     </row>
   </sheetData>

--- a/reports/report.xlsx
+++ b/reports/report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,97 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40.61953580006957</v>
+        <v>39.7477360998746</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tests/test_genz_categories.py::TestGENZCategories::test_mens_tshirts_positive</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>23.68959269998595</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tests/test_genz_categories.py::TestGENZCategories::test_mens_kurtas_positive</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>29.06557719991542</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tests/test_genz_categories.py::TestGENZCategories::test_mens_shoes_positive</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>30.37793050007895</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tests/test_genz_categories.py::TestGENZCategories::test_skincare_positive</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>28.90377990016714</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>tests/test_genz_categories.py::TestGENZCategories::test_jewellery_negative</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>28.22986209997907</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tests/test_genz_categories.py::TestGENZCategories::test_heels_negative</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>passed</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>29.80793930008076</v>
       </c>
     </row>
   </sheetData>
